--- a/Excel/SkillDivineConfig.xlsx
+++ b/Excel/SkillDivineConfig.xlsx
@@ -1057,9 +1057,9 @@
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.25" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.25" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
@@ -1157,7 +1157,8 @@
       <c r="H6" s="2">
         <v>25</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1"/>
+      <c r="K6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="1"/>
@@ -1181,7 +1182,8 @@
       <c r="H7" s="2">
         <v>25</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1"/>
+      <c r="K7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L7" s="1"/>
@@ -1205,7 +1207,8 @@
       <c r="H8" s="2">
         <v>25</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1"/>
+      <c r="K8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="L8" s="1"/>
@@ -1229,7 +1232,8 @@
       <c r="H9" s="2">
         <v>50</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1"/>
+      <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L9" s="1"/>
@@ -1253,7 +1257,8 @@
       <c r="H10" s="2">
         <v>50</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1"/>
+      <c r="K10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L10" s="1"/>
@@ -1277,7 +1282,8 @@
       <c r="H11" s="2">
         <v>50</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1"/>
+      <c r="K11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="L11" s="1"/>
@@ -1301,7 +1307,8 @@
       <c r="H12" s="2">
         <v>75</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1"/>
+      <c r="K12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L12" s="1"/>
@@ -1325,7 +1332,8 @@
       <c r="H13" s="2">
         <v>75</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1"/>
+      <c r="K13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L13" s="1"/>
@@ -1349,7 +1357,8 @@
       <c r="H14" s="2">
         <v>75</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="1"/>
+      <c r="K14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="L14" s="1"/>
@@ -1373,7 +1382,8 @@
       <c r="H15" s="2">
         <v>100</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="1"/>
+      <c r="K15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L15" s="1"/>
@@ -1382,56 +1392,60 @@
     <row r="17" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D17" s="1"/>
       <c r="F17" s="1"/>
+      <c r="I17" s="1"/>
       <c r="L17" s="1"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D18" s="1"/>
       <c r="F18" s="1"/>
+      <c r="I18" s="1"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D19" s="1"/>
       <c r="F19" s="1"/>
+      <c r="I19" s="1"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D20" s="1"/>
       <c r="F20" s="1"/>
+      <c r="I20" s="1"/>
       <c r="L20" s="1"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D21" s="1"/>
       <c r="F21" s="1"/>
+      <c r="I21" s="1"/>
       <c r="L21" s="1"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D22" s="1"/>
       <c r="F22" s="1"/>
+      <c r="I22" s="1"/>
       <c r="L22" s="1"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
       <c r="D23" s="1"/>
       <c r="F23" s="1"/>
+      <c r="I23" s="1"/>
       <c r="L23" s="1"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="7:11">
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="7:11">
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="7:11">
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
@@ -1439,63 +1453,62 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="7:9">
+    <row r="28" spans="7:11">
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="7:9">
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="7:11">
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="7:9">
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="7:11">
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="7:9">
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="7:11">
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="7:9">
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="7:11">
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="7:9">
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="7:11">
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="7:9">
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="7:11">
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="7:9">
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="7:11">
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="7:9">
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="7:11">
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="7:9">
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="7:11">
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 D4 E4 F4 G4 H4 D5 E5 F5 G5 C3:C5 L3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:H3 E4:H4 E5:G5 C3:C5 D4:D5 I3:I5 L3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillDivineConfig.xlsx
+++ b/Excel/SkillDivineConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1048,8 +1048,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
+  <dimension ref="C1:K37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="15.25" style="1" customWidth="1"/>
@@ -1057,16 +1057,15 @@
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1"/>
     <row r="2" ht="16" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1088,9 +1087,8 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1112,9 +1110,8 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1136,9 +1133,8 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1157,13 +1153,12 @@
       <c r="H6" s="2">
         <v>25</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="K6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1182,13 +1177,12 @@
       <c r="H7" s="2">
         <v>25</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="K7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1207,13 +1201,12 @@
       <c r="H8" s="2">
         <v>25</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="K8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1232,13 +1225,12 @@
       <c r="H9" s="2">
         <v>50</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="K9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1257,13 +1249,12 @@
       <c r="H10" s="2">
         <v>50</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="K10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1282,13 +1273,12 @@
       <c r="H11" s="2">
         <v>50</v>
       </c>
-      <c r="I11" s="1"/>
-      <c r="K11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1307,13 +1297,12 @@
       <c r="H12" s="2">
         <v>75</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="K12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1332,13 +1321,12 @@
       <c r="H13" s="2">
         <v>75</v>
       </c>
-      <c r="I13" s="1"/>
-      <c r="K13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1357,13 +1345,12 @@
       <c r="H14" s="2">
         <v>75</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="K14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="16" customHeight="1" spans="3:12">
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1382,133 +1369,158 @@
       <c r="H15" s="2">
         <v>100</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="K15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L15" s="1"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16" customHeight="1"/>
-    <row r="17" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+    <row r="17" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="L17" s="1"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="L19" s="1"/>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="L20" s="1"/>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="L21" s="1"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="L22" s="1"/>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="16" customHeight="1" spans="4:12">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="16" customHeight="1" spans="3:11">
       <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="L23" s="1"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="7:11">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16" customHeight="1" spans="3:11">
+      <c r="C24" s="2"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="7:11">
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16" customHeight="1" spans="3:11">
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="7:11">
+    </row>
+    <row r="26" s="1" customFormat="1" ht="16" customHeight="1" spans="3:11">
+      <c r="C26" s="2"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="6:11">
+    </row>
+    <row r="27" s="1" customFormat="1" spans="3:11">
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="7:11">
+    </row>
+    <row r="28" spans="3:11">
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="7:11">
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="3:11">
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="7:11">
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="3:11">
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="7:11">
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="3:11">
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="7:11">
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="3:11">
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="7:11">
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="7:10">
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="7:11">
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="7:10">
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="7:11">
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="7:10">
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="7:11">
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="7:10">
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="7:11">
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="7:10">
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="K37" s="2"/>
+      <c r="J37" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:H3 E4:H4 E5:G5 C3:C5 D4:D5 I3:I5 L3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:D5 E5:G5 K3:K5 C3:D4 E3:H4" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
